--- a/www/download/COUNTRY.WAF.WIOD13.xlsx
+++ b/www/download/COUNTRY.WAF.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - Africa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -692,348 +702,559 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,36 +1288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -1108,331 +1344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -1469,6 +2069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
